--- a/data/nzd0074/nzd0074.xlsx
+++ b/data/nzd0074/nzd0074.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P323"/>
+  <dimension ref="A1:P324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17896,6 +17896,60 @@
         <v>334.97</v>
       </c>
       <c r="P323" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>285.41</v>
+      </c>
+      <c r="C324" t="n">
+        <v>294.92</v>
+      </c>
+      <c r="D324" t="n">
+        <v>305.72</v>
+      </c>
+      <c r="E324" t="n">
+        <v>316.87</v>
+      </c>
+      <c r="F324" t="n">
+        <v>316.21</v>
+      </c>
+      <c r="G324" t="n">
+        <v>317.48</v>
+      </c>
+      <c r="H324" t="n">
+        <v>320.04</v>
+      </c>
+      <c r="I324" t="n">
+        <v>328.79</v>
+      </c>
+      <c r="J324" t="n">
+        <v>327.17</v>
+      </c>
+      <c r="K324" t="n">
+        <v>329.51</v>
+      </c>
+      <c r="L324" t="n">
+        <v>334.41</v>
+      </c>
+      <c r="M324" t="n">
+        <v>346.25</v>
+      </c>
+      <c r="N324" t="n">
+        <v>336.33</v>
+      </c>
+      <c r="O324" t="n">
+        <v>334.8</v>
+      </c>
+      <c r="P324" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17912,7 +17966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B333"/>
+  <dimension ref="A1:B334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21245,6 +21299,16 @@
       </c>
       <c r="B333" t="n">
         <v>0.16</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -21413,28 +21477,28 @@
         <v>0.0716</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3505697719854773</v>
+        <v>0.3399455602576854</v>
       </c>
       <c r="J2" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K2" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08239891053812609</v>
+        <v>0.07752761110942852</v>
       </c>
       <c r="M2" t="n">
-        <v>6.808774534729372</v>
+        <v>6.83601620669719</v>
       </c>
       <c r="N2" t="n">
-        <v>71.21082365565647</v>
+        <v>71.82656988773942</v>
       </c>
       <c r="O2" t="n">
-        <v>8.438650582626138</v>
+        <v>8.47505574540601</v>
       </c>
       <c r="P2" t="n">
-        <v>292.7468330133413</v>
+        <v>292.858708837669</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -21495,28 +21559,28 @@
         <v>0.0572</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4226837148255159</v>
+        <v>0.4119505092731112</v>
       </c>
       <c r="J3" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K3" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1332760276589939</v>
+        <v>0.1266647200840264</v>
       </c>
       <c r="M3" t="n">
-        <v>6.09316787570985</v>
+        <v>6.123484586355698</v>
       </c>
       <c r="N3" t="n">
-        <v>60.45391426694525</v>
+        <v>61.12020906086516</v>
       </c>
       <c r="O3" t="n">
-        <v>7.77521152554355</v>
+        <v>7.817941484870883</v>
       </c>
       <c r="P3" t="n">
-        <v>300.5379902595286</v>
+        <v>300.6510138183224</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -21577,28 +21641,28 @@
         <v>0.0587</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4191195751582358</v>
+        <v>0.4084547941779847</v>
       </c>
       <c r="J4" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K4" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1548105166768563</v>
+        <v>0.1469557832335446</v>
       </c>
       <c r="M4" t="n">
-        <v>5.740360257382004</v>
+        <v>5.771165244890299</v>
       </c>
       <c r="N4" t="n">
-        <v>49.89926407521799</v>
+        <v>50.58738883134956</v>
       </c>
       <c r="O4" t="n">
-        <v>7.063941114931381</v>
+        <v>7.112481200773016</v>
       </c>
       <c r="P4" t="n">
-        <v>311.3209721171242</v>
+        <v>311.433275146658</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -21659,28 +21723,28 @@
         <v>0.0596</v>
       </c>
       <c r="I5" t="n">
-        <v>0.422663128725778</v>
+        <v>0.414537318721783</v>
       </c>
       <c r="J5" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K5" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1739257559256121</v>
+        <v>0.1678547173025445</v>
       </c>
       <c r="M5" t="n">
-        <v>5.409243059303875</v>
+        <v>5.43126092473142</v>
       </c>
       <c r="N5" t="n">
-        <v>44.14774596732148</v>
+        <v>44.50023235690639</v>
       </c>
       <c r="O5" t="n">
-        <v>6.644377018752133</v>
+        <v>6.670849447926883</v>
       </c>
       <c r="P5" t="n">
-        <v>318.4306670815639</v>
+        <v>318.5162340596908</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -21741,28 +21805,28 @@
         <v>0.0629</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3741365269205667</v>
+        <v>0.366016646383893</v>
       </c>
       <c r="J6" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K6" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1452104379902885</v>
+        <v>0.1393268021445671</v>
       </c>
       <c r="M6" t="n">
-        <v>5.41899635903642</v>
+        <v>5.440420287906897</v>
       </c>
       <c r="N6" t="n">
-        <v>42.87323174748352</v>
+        <v>43.22895036440998</v>
       </c>
       <c r="O6" t="n">
-        <v>6.547765401072607</v>
+        <v>6.574872650052621</v>
       </c>
       <c r="P6" t="n">
-        <v>319.0326392463887</v>
+        <v>319.1181437856202</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -21823,28 +21887,28 @@
         <v>0.0572</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2945118632998869</v>
+        <v>0.2864760376909544</v>
       </c>
       <c r="J7" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K7" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1105872364217615</v>
+        <v>0.104687446574084</v>
       </c>
       <c r="M7" t="n">
-        <v>4.838288892523625</v>
+        <v>4.861117702687747</v>
       </c>
       <c r="N7" t="n">
-        <v>36.29681892831707</v>
+        <v>36.66283761553611</v>
       </c>
       <c r="O7" t="n">
-        <v>6.024684135149084</v>
+        <v>6.054984526448941</v>
       </c>
       <c r="P7" t="n">
-        <v>322.2547826753184</v>
+        <v>322.3394020934161</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -21905,28 +21969,28 @@
         <v>0.0582</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2857434196425299</v>
+        <v>0.2775566042959317</v>
       </c>
       <c r="J8" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K8" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1100221852378297</v>
+        <v>0.1037703014569512</v>
       </c>
       <c r="M8" t="n">
-        <v>4.725287931003138</v>
+        <v>4.748082111236824</v>
       </c>
       <c r="N8" t="n">
-        <v>34.3649736835104</v>
+        <v>34.7551198026933</v>
       </c>
       <c r="O8" t="n">
-        <v>5.862164590278099</v>
+        <v>5.895347301278636</v>
       </c>
       <c r="P8" t="n">
-        <v>325.287230806719</v>
+        <v>325.3734401876111</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -21987,28 +22051,28 @@
         <v>0.0604</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3305689727753321</v>
+        <v>0.3222534324559919</v>
       </c>
       <c r="J9" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K9" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1519126199211935</v>
+        <v>0.1443444708782755</v>
       </c>
       <c r="M9" t="n">
-        <v>4.578808642411614</v>
+        <v>4.603616025895429</v>
       </c>
       <c r="N9" t="n">
-        <v>31.74209223460823</v>
+        <v>32.15609610593015</v>
       </c>
       <c r="O9" t="n">
-        <v>5.634012090385344</v>
+        <v>5.670634541736062</v>
       </c>
       <c r="P9" t="n">
-        <v>333.0551273927155</v>
+        <v>333.1426922824027</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -22069,28 +22133,28 @@
         <v>0.0692</v>
       </c>
       <c r="I10" t="n">
-        <v>0.376609966232986</v>
+        <v>0.3683368527947442</v>
       </c>
       <c r="J10" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K10" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1722829125542412</v>
+        <v>0.1650428330482703</v>
       </c>
       <c r="M10" t="n">
-        <v>4.68796583421865</v>
+        <v>4.717350887110431</v>
       </c>
       <c r="N10" t="n">
-        <v>35.45585467303281</v>
+        <v>35.85314677024705</v>
       </c>
       <c r="O10" t="n">
-        <v>5.95448189795156</v>
+        <v>5.987749725084295</v>
       </c>
       <c r="P10" t="n">
-        <v>330.1640853221172</v>
+        <v>330.251203445266</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -22151,28 +22215,28 @@
         <v>0.06469999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3237600858540198</v>
+        <v>0.3142516660850425</v>
       </c>
       <c r="J11" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K11" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1437950371833744</v>
+        <v>0.1350309272294433</v>
       </c>
       <c r="M11" t="n">
-        <v>4.446292212603383</v>
+        <v>4.482921445126137</v>
       </c>
       <c r="N11" t="n">
-        <v>32.47469509898713</v>
+        <v>33.0439467254275</v>
       </c>
       <c r="O11" t="n">
-        <v>5.698657306680857</v>
+        <v>5.748386445379913</v>
       </c>
       <c r="P11" t="n">
-        <v>335.8081271642137</v>
+        <v>335.90825339729</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -22233,28 +22297,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.288487289811281</v>
+        <v>0.2792091652429996</v>
       </c>
       <c r="J12" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K12" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1229306343053616</v>
+        <v>0.1146789374297752</v>
       </c>
       <c r="M12" t="n">
-        <v>4.458083379339284</v>
+        <v>4.494402621898272</v>
       </c>
       <c r="N12" t="n">
-        <v>30.89525705231191</v>
+        <v>31.43734656295421</v>
       </c>
       <c r="O12" t="n">
-        <v>5.55835020957765</v>
+        <v>5.606901690145299</v>
       </c>
       <c r="P12" t="n">
-        <v>341.2790720154434</v>
+        <v>341.3767731777402</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -22315,28 +22379,28 @@
         <v>0.06759999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2555679499461467</v>
+        <v>0.2474990318037678</v>
       </c>
       <c r="J13" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K13" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L13" t="n">
-        <v>0.08106100665953786</v>
+        <v>0.07602411127318121</v>
       </c>
       <c r="M13" t="n">
-        <v>4.939412647920324</v>
+        <v>4.96658635364482</v>
       </c>
       <c r="N13" t="n">
-        <v>38.5258378019978</v>
+        <v>38.88890377712748</v>
       </c>
       <c r="O13" t="n">
-        <v>6.206918543206267</v>
+        <v>6.236096838337862</v>
       </c>
       <c r="P13" t="n">
-        <v>352.0963987369412</v>
+        <v>352.1813666283707</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -22397,28 +22461,28 @@
         <v>0.0663</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1356466800408554</v>
+        <v>0.1270740173092623</v>
       </c>
       <c r="J14" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K14" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02224941244624468</v>
+        <v>0.01946695370834728</v>
       </c>
       <c r="M14" t="n">
-        <v>5.206811268480724</v>
+        <v>5.235223513138989</v>
       </c>
       <c r="N14" t="n">
-        <v>42.0719364961979</v>
+        <v>42.48612912096768</v>
       </c>
       <c r="O14" t="n">
-        <v>6.486288345132206</v>
+        <v>6.518138470527278</v>
       </c>
       <c r="P14" t="n">
-        <v>346.1050267492018</v>
+        <v>346.1952992074654</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -22479,28 +22543,28 @@
         <v>0.0717</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2220987393395013</v>
+        <v>0.2124143963105163</v>
       </c>
       <c r="J15" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K15" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04850073739967653</v>
+        <v>0.04426245170584475</v>
       </c>
       <c r="M15" t="n">
-        <v>5.742350636115678</v>
+        <v>5.77790632484938</v>
       </c>
       <c r="N15" t="n">
-        <v>50.35202336452002</v>
+        <v>50.89094129386356</v>
       </c>
       <c r="O15" t="n">
-        <v>7.095915963744217</v>
+        <v>7.133788705440018</v>
       </c>
       <c r="P15" t="n">
-        <v>344.0387406735839</v>
+        <v>344.1407194261915</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -22542,7 +22606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P323"/>
+  <dimension ref="A1:P324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49031,6 +49095,88 @@
         </is>
       </c>
     </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>-35.440588340285004,174.41416219570976</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>-35.44031235316885,174.41499985638998</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>-35.44002109994008,174.41585117647645</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>-35.439677830834896,174.41671048631937</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>-35.43933453439993,174.4175530613131</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>-35.438967105086206,174.41835132657064</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>-35.43856027288369,174.41911334117603</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>-35.438095660061514,174.41985782102324</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>-35.4375951925431,174.42056393807457</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>-35.437067513784974,174.4212133696808</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>-35.436483773202376,174.4217858049334</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>-35.435842326545995,174.42229401447213</t>
+        </is>
+      </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>-35.43518070060909,174.4227603485781</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>-35.434506982913184,174.4231162751299</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0074/nzd0074.xlsx
+++ b/data/nzd0074/nzd0074.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P324"/>
+  <dimension ref="A1:P326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17950,6 +17950,114 @@
         <v>334.8</v>
       </c>
       <c r="P324" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>284.05</v>
+      </c>
+      <c r="C325" t="n">
+        <v>292.01</v>
+      </c>
+      <c r="D325" t="n">
+        <v>303.28</v>
+      </c>
+      <c r="E325" t="n">
+        <v>314.64</v>
+      </c>
+      <c r="F325" t="n">
+        <v>314.18</v>
+      </c>
+      <c r="G325" t="n">
+        <v>316.4</v>
+      </c>
+      <c r="H325" t="n">
+        <v>318.83</v>
+      </c>
+      <c r="I325" t="n">
+        <v>327.5</v>
+      </c>
+      <c r="J325" t="n">
+        <v>325.74</v>
+      </c>
+      <c r="K325" t="n">
+        <v>328.32</v>
+      </c>
+      <c r="L325" t="n">
+        <v>332.8</v>
+      </c>
+      <c r="M325" t="n">
+        <v>345.96</v>
+      </c>
+      <c r="N325" t="n">
+        <v>335.8</v>
+      </c>
+      <c r="O325" t="n">
+        <v>333.91</v>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>283.94</v>
+      </c>
+      <c r="C326" t="n">
+        <v>292.61</v>
+      </c>
+      <c r="D326" t="n">
+        <v>303.51</v>
+      </c>
+      <c r="E326" t="n">
+        <v>315.23</v>
+      </c>
+      <c r="F326" t="n">
+        <v>314.27</v>
+      </c>
+      <c r="G326" t="n">
+        <v>315.75</v>
+      </c>
+      <c r="H326" t="n">
+        <v>318.13</v>
+      </c>
+      <c r="I326" t="n">
+        <v>327.7</v>
+      </c>
+      <c r="J326" t="n">
+        <v>325.19</v>
+      </c>
+      <c r="K326" t="n">
+        <v>328.71</v>
+      </c>
+      <c r="L326" t="n">
+        <v>332.88</v>
+      </c>
+      <c r="M326" t="n">
+        <v>346.14</v>
+      </c>
+      <c r="N326" t="n">
+        <v>336.22</v>
+      </c>
+      <c r="O326" t="n">
+        <v>334.53</v>
+      </c>
+      <c r="P326" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17966,7 +18074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B334"/>
+  <dimension ref="A1:B336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21309,6 +21417,26 @@
       </c>
       <c r="B334" t="n">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>0.64</v>
       </c>
     </row>
   </sheetData>
@@ -21477,28 +21605,28 @@
         <v>0.0716</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3399455602576854</v>
+        <v>0.317272271694448</v>
       </c>
       <c r="J2" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K2" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07752761110942852</v>
+        <v>0.06743022818563593</v>
       </c>
       <c r="M2" t="n">
-        <v>6.83601620669719</v>
+        <v>6.896879444609552</v>
       </c>
       <c r="N2" t="n">
-        <v>71.82656988773942</v>
+        <v>73.29662681710346</v>
       </c>
       <c r="O2" t="n">
-        <v>8.47505574540601</v>
+        <v>8.561344918708944</v>
       </c>
       <c r="P2" t="n">
-        <v>292.858708837669</v>
+        <v>293.0985558517797</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -21559,28 +21687,28 @@
         <v>0.0572</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4119505092731112</v>
+        <v>0.3875297321040217</v>
       </c>
       <c r="J3" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K3" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1266647200840264</v>
+        <v>0.1115686606120321</v>
       </c>
       <c r="M3" t="n">
-        <v>6.123484586355698</v>
+        <v>6.199059136730747</v>
       </c>
       <c r="N3" t="n">
-        <v>61.12020906086516</v>
+        <v>62.96290449697625</v>
       </c>
       <c r="O3" t="n">
-        <v>7.817941484870883</v>
+        <v>7.934916792063811</v>
       </c>
       <c r="P3" t="n">
-        <v>300.6510138183224</v>
+        <v>300.9093420160213</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -21641,28 +21769,28 @@
         <v>0.0587</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4084547941779847</v>
+        <v>0.3845368399281895</v>
       </c>
       <c r="J4" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K4" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1469557832335446</v>
+        <v>0.1293453235223143</v>
       </c>
       <c r="M4" t="n">
-        <v>5.771165244890299</v>
+        <v>5.845164526293741</v>
       </c>
       <c r="N4" t="n">
-        <v>50.58738883134956</v>
+        <v>52.40396632211131</v>
       </c>
       <c r="O4" t="n">
-        <v>7.112481200773016</v>
+        <v>7.239058386427844</v>
       </c>
       <c r="P4" t="n">
-        <v>311.433275146658</v>
+        <v>311.686286541964</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -21723,28 +21851,28 @@
         <v>0.0596</v>
       </c>
       <c r="I5" t="n">
-        <v>0.414537318721783</v>
+        <v>0.396095636158811</v>
       </c>
       <c r="J5" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K5" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1678547173025445</v>
+        <v>0.1536727932508635</v>
       </c>
       <c r="M5" t="n">
-        <v>5.43126092473142</v>
+        <v>5.485383279683306</v>
       </c>
       <c r="N5" t="n">
-        <v>44.50023235690639</v>
+        <v>45.49194230335139</v>
       </c>
       <c r="O5" t="n">
-        <v>6.670849447926883</v>
+        <v>6.74477147895697</v>
       </c>
       <c r="P5" t="n">
-        <v>318.5162340596908</v>
+        <v>318.7113133070653</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -21805,28 +21933,28 @@
         <v>0.0629</v>
       </c>
       <c r="I6" t="n">
-        <v>0.366016646383893</v>
+        <v>0.3475269368216332</v>
       </c>
       <c r="J6" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K6" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1393268021445671</v>
+        <v>0.1256833048205569</v>
       </c>
       <c r="M6" t="n">
-        <v>5.440420287906897</v>
+        <v>5.493509742328665</v>
       </c>
       <c r="N6" t="n">
-        <v>43.22895036440998</v>
+        <v>44.23450498003032</v>
       </c>
       <c r="O6" t="n">
-        <v>6.574872650052621</v>
+        <v>6.650902568827055</v>
       </c>
       <c r="P6" t="n">
-        <v>319.1181437856202</v>
+        <v>319.3137340980275</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -21887,28 +22015,28 @@
         <v>0.0572</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2864760376909544</v>
+        <v>0.2689028529573557</v>
       </c>
       <c r="J7" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K7" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L7" t="n">
-        <v>0.104687446574084</v>
+        <v>0.09197139954359279</v>
       </c>
       <c r="M7" t="n">
-        <v>4.861117702687747</v>
+        <v>4.915333473751404</v>
       </c>
       <c r="N7" t="n">
-        <v>36.66283761553611</v>
+        <v>37.586388612505</v>
       </c>
       <c r="O7" t="n">
-        <v>6.054984526448941</v>
+        <v>6.130773899966056</v>
       </c>
       <c r="P7" t="n">
-        <v>322.3394020934161</v>
+        <v>322.5253016386754</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -21969,28 +22097,28 @@
         <v>0.0582</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2775566042959317</v>
+        <v>0.2594832515165808</v>
       </c>
       <c r="J8" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K8" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1037703014569512</v>
+        <v>0.09019850008216701</v>
       </c>
       <c r="M8" t="n">
-        <v>4.748082111236824</v>
+        <v>4.800741043807688</v>
       </c>
       <c r="N8" t="n">
-        <v>34.7551198026933</v>
+        <v>35.75683271247902</v>
       </c>
       <c r="O8" t="n">
-        <v>5.895347301278636</v>
+        <v>5.979701724373801</v>
       </c>
       <c r="P8" t="n">
-        <v>325.3734401876111</v>
+        <v>325.5646310459089</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -22051,28 +22179,28 @@
         <v>0.0604</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3222534324559919</v>
+        <v>0.3044026302186896</v>
       </c>
       <c r="J9" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K9" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1443444708782755</v>
+        <v>0.1283082319861888</v>
       </c>
       <c r="M9" t="n">
-        <v>4.603616025895429</v>
+        <v>4.658925522792205</v>
       </c>
       <c r="N9" t="n">
-        <v>32.15609610593015</v>
+        <v>33.14349266886683</v>
       </c>
       <c r="O9" t="n">
-        <v>5.670634541736062</v>
+        <v>5.75703853286278</v>
       </c>
       <c r="P9" t="n">
-        <v>333.1426922824027</v>
+        <v>333.3315233652773</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -22133,28 +22261,28 @@
         <v>0.0692</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3683368527947442</v>
+        <v>0.3499061791502873</v>
       </c>
       <c r="J10" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K10" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1650428330482703</v>
+        <v>0.1487246177509768</v>
       </c>
       <c r="M10" t="n">
-        <v>4.717350887110431</v>
+        <v>4.786498075862848</v>
       </c>
       <c r="N10" t="n">
-        <v>35.85314677024705</v>
+        <v>36.89635668877411</v>
       </c>
       <c r="O10" t="n">
-        <v>5.987749725084295</v>
+        <v>6.074237128131739</v>
       </c>
       <c r="P10" t="n">
-        <v>330.251203445266</v>
+        <v>330.446173282994</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -22215,28 +22343,28 @@
         <v>0.06469999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3142516660850425</v>
+        <v>0.2943063773174234</v>
       </c>
       <c r="J11" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K11" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1350309272294433</v>
+        <v>0.1172889285038616</v>
       </c>
       <c r="M11" t="n">
-        <v>4.482921445126137</v>
+        <v>4.560436301036643</v>
       </c>
       <c r="N11" t="n">
-        <v>33.0439467254275</v>
+        <v>34.32052701135144</v>
       </c>
       <c r="O11" t="n">
-        <v>5.748386445379913</v>
+        <v>5.858372385855259</v>
       </c>
       <c r="P11" t="n">
-        <v>335.90825339729</v>
+        <v>336.119239529862</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -22297,28 +22425,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2792091652429996</v>
+        <v>0.2589854052231389</v>
       </c>
       <c r="J12" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K12" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1146789374297752</v>
+        <v>0.09729233254367275</v>
       </c>
       <c r="M12" t="n">
-        <v>4.494402621898272</v>
+        <v>4.577292493556733</v>
       </c>
       <c r="N12" t="n">
-        <v>31.43734656295421</v>
+        <v>32.76514878039309</v>
       </c>
       <c r="O12" t="n">
-        <v>5.606901690145299</v>
+        <v>5.72408497319817</v>
       </c>
       <c r="P12" t="n">
-        <v>341.3767731777402</v>
+        <v>341.5907069879173</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -22379,28 +22507,28 @@
         <v>0.06759999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2474990318037678</v>
+        <v>0.2314075146594123</v>
       </c>
       <c r="J13" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K13" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L13" t="n">
-        <v>0.07602411127318121</v>
+        <v>0.06644365106889383</v>
       </c>
       <c r="M13" t="n">
-        <v>4.96658635364482</v>
+        <v>5.02073209488777</v>
       </c>
       <c r="N13" t="n">
-        <v>38.88890377712748</v>
+        <v>39.61275165290669</v>
       </c>
       <c r="O13" t="n">
-        <v>6.236096838337862</v>
+        <v>6.293866192802854</v>
       </c>
       <c r="P13" t="n">
-        <v>352.1813666283707</v>
+        <v>352.3515874554461</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -22461,28 +22589,28 @@
         <v>0.0663</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1270740173092623</v>
+        <v>0.109849531468546</v>
       </c>
       <c r="J14" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K14" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01946695370834728</v>
+        <v>0.0144508749411737</v>
       </c>
       <c r="M14" t="n">
-        <v>5.235223513138989</v>
+        <v>5.294448848955452</v>
       </c>
       <c r="N14" t="n">
-        <v>42.48612912096768</v>
+        <v>43.32849448943954</v>
       </c>
       <c r="O14" t="n">
-        <v>6.518138470527278</v>
+        <v>6.582438339205278</v>
       </c>
       <c r="P14" t="n">
-        <v>346.1952992074654</v>
+        <v>346.3775034756827</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -22543,28 +22671,28 @@
         <v>0.0717</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2124143963105163</v>
+        <v>0.19266783854846</v>
       </c>
       <c r="J15" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K15" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04426245170584475</v>
+        <v>0.03620372891787749</v>
       </c>
       <c r="M15" t="n">
-        <v>5.77790632484938</v>
+        <v>5.851142305700782</v>
       </c>
       <c r="N15" t="n">
-        <v>50.89094129386356</v>
+        <v>52.02875515551651</v>
       </c>
       <c r="O15" t="n">
-        <v>7.133788705440018</v>
+        <v>7.213096086668783</v>
       </c>
       <c r="P15" t="n">
-        <v>344.1407194261915</v>
+        <v>344.3496018600607</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -22606,7 +22734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P324"/>
+  <dimension ref="A1:P326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49177,6 +49305,170 @@
         </is>
       </c>
     </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>-35.440600132239275,174.4141662971179</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>-35.44033758443936,174.41500863233063</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>-35.4400420715571,174.41585928528255</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>-35.43969627059435,174.41672027094273</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>-35.439350628047336,174.41756370666738</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>-35.438975484670536,174.41835738405828</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>-35.43856951834369,174.4191204143768</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>-35.43810489301243,174.41986646063475</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>-35.437604563576826,174.4205747553068</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>-35.43707493125279,174.42122283970997</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>-35.43649326595582,174.42179922045466</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>-35.43584368599653,174.42229674302442</t>
+        </is>
+      </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>-35.43518249088121,174.42276576126096</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>-35.434509942442425,174.42312538716544</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>-35.440601086000264,174.4141666288495</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>-35.44033238211561,174.41500682285786</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>-35.44004009472438,174.4158585209277</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>-35.4396913919137,174.41671768218544</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>-35.439349914535875,174.41756323470574</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>-35.43898052793873,174.41836102976904</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>-35.43857486695671,174.41912450631187</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>-35.43810346154722,174.41986512115997</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>-35.43760816782029,174.42057891578142</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>-35.43707250031805,174.42121973608675</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>-35.43649279426626,174.4217985538448</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>-35.435842842199655,174.42229504944024</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>-35.435181072175006,174.4227614719651</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>-35.43450788074797,174.42311903945523</t>
+        </is>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0074/nzd0074.xlsx
+++ b/data/nzd0074/nzd0074.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P326"/>
+  <dimension ref="A1:P328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18060,6 +18060,114 @@
       <c r="P326" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>288.07</v>
+      </c>
+      <c r="C327" t="n">
+        <v>296.83</v>
+      </c>
+      <c r="D327" t="n">
+        <v>307.85</v>
+      </c>
+      <c r="E327" t="n">
+        <v>320.13</v>
+      </c>
+      <c r="F327" t="n">
+        <v>320.11</v>
+      </c>
+      <c r="G327" t="n">
+        <v>321.38</v>
+      </c>
+      <c r="H327" t="n">
+        <v>324.52</v>
+      </c>
+      <c r="I327" t="n">
+        <v>334.7</v>
+      </c>
+      <c r="J327" t="n">
+        <v>330.85</v>
+      </c>
+      <c r="K327" t="n">
+        <v>334.63</v>
+      </c>
+      <c r="L327" t="n">
+        <v>338.59</v>
+      </c>
+      <c r="M327" t="n">
+        <v>351.13</v>
+      </c>
+      <c r="N327" t="n">
+        <v>341.92</v>
+      </c>
+      <c r="O327" t="n">
+        <v>340.37</v>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>288.07</v>
+      </c>
+      <c r="C328" t="n">
+        <v>296.83</v>
+      </c>
+      <c r="D328" t="n">
+        <v>307.85</v>
+      </c>
+      <c r="E328" t="n">
+        <v>321.57</v>
+      </c>
+      <c r="F328" t="n">
+        <v>321.62</v>
+      </c>
+      <c r="G328" t="n">
+        <v>323.23</v>
+      </c>
+      <c r="H328" t="n">
+        <v>325.53</v>
+      </c>
+      <c r="I328" t="n">
+        <v>336.32</v>
+      </c>
+      <c r="J328" t="n">
+        <v>331.61</v>
+      </c>
+      <c r="K328" t="n">
+        <v>335.92</v>
+      </c>
+      <c r="L328" t="n">
+        <v>340.27</v>
+      </c>
+      <c r="M328" t="n">
+        <v>351.99</v>
+      </c>
+      <c r="N328" t="n">
+        <v>343.23</v>
+      </c>
+      <c r="O328" t="n">
+        <v>341.53</v>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -18074,7 +18182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B336"/>
+  <dimension ref="A1:B338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21437,6 +21545,26 @@
       </c>
       <c r="B336" t="n">
         <v>0.64</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -21605,28 +21733,28 @@
         <v>0.0716</v>
       </c>
       <c r="I2" t="n">
-        <v>0.317272271694448</v>
+        <v>0.3003672659864437</v>
       </c>
       <c r="J2" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K2" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06743022818563593</v>
+        <v>0.06082032520624536</v>
       </c>
       <c r="M2" t="n">
-        <v>6.896879444609552</v>
+        <v>6.93072544374532</v>
       </c>
       <c r="N2" t="n">
-        <v>73.29662681710346</v>
+        <v>73.92645126773748</v>
       </c>
       <c r="O2" t="n">
-        <v>8.561344918708944</v>
+        <v>8.598049271069426</v>
       </c>
       <c r="P2" t="n">
-        <v>293.0985558517797</v>
+        <v>293.278196301332</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -21687,28 +21815,28 @@
         <v>0.0572</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3875297321040217</v>
+        <v>0.3694857903692155</v>
       </c>
       <c r="J3" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K3" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1115686606120321</v>
+        <v>0.1019587058533318</v>
       </c>
       <c r="M3" t="n">
-        <v>6.199059136730747</v>
+        <v>6.246755325620709</v>
       </c>
       <c r="N3" t="n">
-        <v>62.96290449697625</v>
+        <v>63.80609753720282</v>
       </c>
       <c r="O3" t="n">
-        <v>7.934916792063811</v>
+        <v>7.987871902903978</v>
       </c>
       <c r="P3" t="n">
-        <v>300.9093420160213</v>
+        <v>301.1010853423844</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -21769,28 +21897,28 @@
         <v>0.0587</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3845368399281895</v>
+        <v>0.3669025353193092</v>
       </c>
       <c r="J4" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K4" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1293453235223143</v>
+        <v>0.1182660838143993</v>
       </c>
       <c r="M4" t="n">
-        <v>5.845164526293741</v>
+        <v>5.891289248480109</v>
       </c>
       <c r="N4" t="n">
-        <v>52.40396632211131</v>
+        <v>53.25660340093432</v>
       </c>
       <c r="O4" t="n">
-        <v>7.239058386427844</v>
+        <v>7.297712203213711</v>
       </c>
       <c r="P4" t="n">
-        <v>311.686286541964</v>
+        <v>311.8736768750522</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -21851,28 +21979,28 @@
         <v>0.0596</v>
       </c>
       <c r="I5" t="n">
-        <v>0.396095636158811</v>
+        <v>0.3856064779518445</v>
       </c>
       <c r="J5" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K5" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1536727932508635</v>
+        <v>0.1474178904452984</v>
       </c>
       <c r="M5" t="n">
-        <v>5.485383279683306</v>
+        <v>5.502526219308815</v>
       </c>
       <c r="N5" t="n">
-        <v>45.49194230335139</v>
+        <v>45.63198637681529</v>
       </c>
       <c r="O5" t="n">
-        <v>6.74477147895697</v>
+        <v>6.755145178070956</v>
       </c>
       <c r="P5" t="n">
-        <v>318.7113133070653</v>
+        <v>318.8227672462691</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -21933,28 +22061,28 @@
         <v>0.0629</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3475269368216332</v>
+        <v>0.337909987486359</v>
       </c>
       <c r="J6" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K6" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1256833048205569</v>
+        <v>0.1202758395209468</v>
       </c>
       <c r="M6" t="n">
-        <v>5.493509742328665</v>
+        <v>5.505317442576069</v>
       </c>
       <c r="N6" t="n">
-        <v>44.23450498003032</v>
+        <v>44.31644225602758</v>
       </c>
       <c r="O6" t="n">
-        <v>6.650902568827055</v>
+        <v>6.657059580327306</v>
       </c>
       <c r="P6" t="n">
-        <v>319.3137340980275</v>
+        <v>319.4159190427643</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -22015,28 +22143,28 @@
         <v>0.0572</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2689028529573557</v>
+        <v>0.2596755270468147</v>
       </c>
       <c r="J7" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K7" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09197139954359279</v>
+        <v>0.08671917387932193</v>
       </c>
       <c r="M7" t="n">
-        <v>4.915333473751404</v>
+        <v>4.929588303634196</v>
       </c>
       <c r="N7" t="n">
-        <v>37.586388612505</v>
+        <v>37.68304250784269</v>
       </c>
       <c r="O7" t="n">
-        <v>6.130773899966056</v>
+        <v>6.138651521942151</v>
       </c>
       <c r="P7" t="n">
-        <v>322.5253016386754</v>
+        <v>322.6233441895928</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -22097,28 +22225,28 @@
         <v>0.0582</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2594832515165808</v>
+        <v>0.250167560546584</v>
       </c>
       <c r="J8" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K8" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09019850008216701</v>
+        <v>0.08474282935027777</v>
       </c>
       <c r="M8" t="n">
-        <v>4.800741043807688</v>
+        <v>4.814527527271404</v>
       </c>
       <c r="N8" t="n">
-        <v>35.75683271247902</v>
+        <v>35.86715059067126</v>
       </c>
       <c r="O8" t="n">
-        <v>5.979701724373801</v>
+        <v>5.988918983478676</v>
       </c>
       <c r="P8" t="n">
-        <v>325.5646310459089</v>
+        <v>325.663617731466</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -22179,28 +22307,28 @@
         <v>0.0604</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3044026302186896</v>
+        <v>0.2970123531526984</v>
       </c>
       <c r="J9" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K9" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1283082319861888</v>
+        <v>0.1237328081968534</v>
       </c>
       <c r="M9" t="n">
-        <v>4.658925522792205</v>
+        <v>4.664964075179255</v>
       </c>
       <c r="N9" t="n">
-        <v>33.14349266886683</v>
+        <v>33.15090706484192</v>
       </c>
       <c r="O9" t="n">
-        <v>5.75703853286278</v>
+        <v>5.757682438693708</v>
       </c>
       <c r="P9" t="n">
-        <v>333.3315233652773</v>
+        <v>333.4100459812608</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -22261,28 +22389,28 @@
         <v>0.0692</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3499061791502873</v>
+        <v>0.3392442597171384</v>
       </c>
       <c r="J10" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K10" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1487246177509768</v>
+        <v>0.1413389931012993</v>
       </c>
       <c r="M10" t="n">
-        <v>4.786498075862848</v>
+        <v>4.815708737516428</v>
       </c>
       <c r="N10" t="n">
-        <v>36.89635668877411</v>
+        <v>37.10047522626132</v>
       </c>
       <c r="O10" t="n">
-        <v>6.074237128131739</v>
+        <v>6.091015943687992</v>
       </c>
       <c r="P10" t="n">
-        <v>330.446173282994</v>
+        <v>330.5594671645045</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -22343,28 +22471,28 @@
         <v>0.06469999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2943063773174234</v>
+        <v>0.2834465560765259</v>
       </c>
       <c r="J11" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K11" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1172889285038616</v>
+        <v>0.1098160550705977</v>
       </c>
       <c r="M11" t="n">
-        <v>4.560436301036643</v>
+        <v>4.589358186008998</v>
       </c>
       <c r="N11" t="n">
-        <v>34.32052701135144</v>
+        <v>34.55819068940097</v>
       </c>
       <c r="O11" t="n">
-        <v>5.858372385855259</v>
+        <v>5.878621495674047</v>
       </c>
       <c r="P11" t="n">
-        <v>336.119239529862</v>
+        <v>336.2346331230275</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -22425,28 +22553,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2589854052231389</v>
+        <v>0.2476423438851025</v>
       </c>
       <c r="J12" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K12" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L12" t="n">
-        <v>0.09729233254367275</v>
+        <v>0.08962580557252731</v>
       </c>
       <c r="M12" t="n">
-        <v>4.577292493556733</v>
+        <v>4.611851245232446</v>
       </c>
       <c r="N12" t="n">
-        <v>32.76514878039309</v>
+        <v>33.05456048931903</v>
       </c>
       <c r="O12" t="n">
-        <v>5.72408497319817</v>
+        <v>5.749309566314814</v>
       </c>
       <c r="P12" t="n">
-        <v>341.5907069879173</v>
+        <v>341.7112333877532</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -22507,28 +22635,28 @@
         <v>0.06759999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2314075146594123</v>
+        <v>0.2227049228688227</v>
       </c>
       <c r="J13" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K13" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L13" t="n">
-        <v>0.06644365106889383</v>
+        <v>0.06223364805414089</v>
       </c>
       <c r="M13" t="n">
-        <v>5.02073209488777</v>
+        <v>5.035542623393758</v>
       </c>
       <c r="N13" t="n">
-        <v>39.61275165290669</v>
+        <v>39.65735356903618</v>
       </c>
       <c r="O13" t="n">
-        <v>6.293866192802854</v>
+        <v>6.297408480401774</v>
       </c>
       <c r="P13" t="n">
-        <v>352.3515874554461</v>
+        <v>352.4440600166358</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -22589,28 +22717,28 @@
         <v>0.0663</v>
       </c>
       <c r="I14" t="n">
-        <v>0.109849531468546</v>
+        <v>0.1013969418365065</v>
       </c>
       <c r="J14" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K14" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0144508749411737</v>
+        <v>0.01243268517145313</v>
       </c>
       <c r="M14" t="n">
-        <v>5.294448848955452</v>
+        <v>5.306556474683248</v>
       </c>
       <c r="N14" t="n">
-        <v>43.32849448943954</v>
+        <v>43.33573767971961</v>
       </c>
       <c r="O14" t="n">
-        <v>6.582438339205278</v>
+        <v>6.582988506728507</v>
       </c>
       <c r="P14" t="n">
-        <v>346.3775034756827</v>
+        <v>346.467316584009</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -22671,28 +22799,28 @@
         <v>0.0717</v>
       </c>
       <c r="I15" t="n">
-        <v>0.19266783854846</v>
+        <v>0.1819745643163033</v>
       </c>
       <c r="J15" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K15" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03620372891787749</v>
+        <v>0.03259997699322081</v>
       </c>
       <c r="M15" t="n">
-        <v>5.851142305700782</v>
+        <v>5.874302033435</v>
       </c>
       <c r="N15" t="n">
-        <v>52.02875515551651</v>
+        <v>52.14406506977437</v>
       </c>
       <c r="O15" t="n">
-        <v>7.213096086668783</v>
+        <v>7.221084757138249</v>
       </c>
       <c r="P15" t="n">
-        <v>344.3496018600607</v>
+        <v>344.4632264520606</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -22734,7 +22862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P326"/>
+  <dimension ref="A1:P328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49469,6 +49597,170 @@
         </is>
       </c>
     </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>-35.44056527660917,174.41415417384155</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>-35.44029579243753,174.41499409623964</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>-35.440002792749254,174.4158440978911</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>-35.43965087405479,174.41669618234906</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>-35.43930361556691,174.41753260965942</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>-35.43893684547325,174.41832945232028</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>-35.43852604175494,174.41908715281062</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>-35.438053360254486,174.4198182395726</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>-35.437571076871116,174.4205361007332</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>-35.437035599964865,174.42117262470126</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>-35.436459127412746,174.42175097458852</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>-35.43581945026537,174.42224809953655</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>-35.43516181828976,174.42270326010708</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>-35.43448846089965,174.42305924813581</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>-35.44056527660917,174.41415417384155</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>-35.44029579243753,174.41499409623964</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>-35.440002792749254,174.4158440978911</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>-35.43963896676477,174.41668986403405</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>-35.439291644427925,174.41752469120289</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>-35.43892249155271,174.41831907607914</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>-35.43851832446835,174.41908124874027</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>-35.438041765381044,174.41980738984216</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>-35.43756609645972,174.4205303517191</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>-35.437027559175846,174.4211623588814</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>-35.43644922192493,174.42173697579554</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>-35.4358154187878,174.4222400079727</t>
+        </is>
+      </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>-35.435157393269954,174.42268988159614</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>-35.434484603528915,174.42304737178117</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0074/nzd0074.xlsx
+++ b/data/nzd0074/nzd0074.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P328"/>
+  <dimension ref="A1:P329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18166,6 +18166,60 @@
         <v>341.53</v>
       </c>
       <c r="P328" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>288.43</v>
+      </c>
+      <c r="C329" t="n">
+        <v>296.77</v>
+      </c>
+      <c r="D329" t="n">
+        <v>308.5</v>
+      </c>
+      <c r="E329" t="n">
+        <v>322.23</v>
+      </c>
+      <c r="F329" t="n">
+        <v>323.17</v>
+      </c>
+      <c r="G329" t="n">
+        <v>325.76</v>
+      </c>
+      <c r="H329" t="n">
+        <v>327.7</v>
+      </c>
+      <c r="I329" t="n">
+        <v>338.26</v>
+      </c>
+      <c r="J329" t="n">
+        <v>332.81</v>
+      </c>
+      <c r="K329" t="n">
+        <v>338.41</v>
+      </c>
+      <c r="L329" t="n">
+        <v>341.96</v>
+      </c>
+      <c r="M329" t="n">
+        <v>353.47</v>
+      </c>
+      <c r="N329" t="n">
+        <v>345.2</v>
+      </c>
+      <c r="O329" t="n">
+        <v>342.75</v>
+      </c>
+      <c r="P329" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -18182,7 +18236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B338"/>
+  <dimension ref="A1:B339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21565,6 +21619,16 @@
       </c>
       <c r="B338" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>0.97</v>
       </c>
     </row>
   </sheetData>
@@ -21733,28 +21797,28 @@
         <v>0.0716</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3003672659864437</v>
+        <v>0.2923281490942704</v>
       </c>
       <c r="J2" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K2" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06082032520624536</v>
+        <v>0.05780677962606839</v>
       </c>
       <c r="M2" t="n">
-        <v>6.93072544374532</v>
+        <v>6.945751747697572</v>
       </c>
       <c r="N2" t="n">
-        <v>73.92645126773748</v>
+        <v>74.19608475627825</v>
       </c>
       <c r="O2" t="n">
-        <v>8.598049271069426</v>
+        <v>8.613714921929924</v>
       </c>
       <c r="P2" t="n">
-        <v>293.278196301332</v>
+        <v>293.3638566155071</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -21815,28 +21879,28 @@
         <v>0.0572</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3694857903692155</v>
+        <v>0.3606227312688297</v>
       </c>
       <c r="J3" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K3" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1019587058533318</v>
+        <v>0.09737902865459824</v>
       </c>
       <c r="M3" t="n">
-        <v>6.246755325620709</v>
+        <v>6.269840903832529</v>
       </c>
       <c r="N3" t="n">
-        <v>63.80609753720282</v>
+        <v>64.21325631936371</v>
       </c>
       <c r="O3" t="n">
-        <v>7.987871902903978</v>
+        <v>8.013317435329997</v>
       </c>
       <c r="P3" t="n">
-        <v>301.1010853423844</v>
+        <v>301.1955251219367</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -21897,28 +21961,28 @@
         <v>0.0587</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3669025353193092</v>
+        <v>0.3586834397178385</v>
       </c>
       <c r="J4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1182660838143993</v>
+        <v>0.1133436466664506</v>
       </c>
       <c r="M4" t="n">
-        <v>5.891289248480109</v>
+        <v>5.911349051592515</v>
       </c>
       <c r="N4" t="n">
-        <v>53.25660340093432</v>
+        <v>53.61166767334182</v>
       </c>
       <c r="O4" t="n">
-        <v>7.297712203213711</v>
+        <v>7.321998885095642</v>
       </c>
       <c r="P4" t="n">
-        <v>311.8736768750522</v>
+        <v>311.9612549412628</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -21979,28 +22043,28 @@
         <v>0.0596</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3856064779518445</v>
+        <v>0.3813353252334165</v>
       </c>
       <c r="J5" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K5" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1474178904452984</v>
+        <v>0.1451186575622336</v>
       </c>
       <c r="M5" t="n">
-        <v>5.502526219308815</v>
+        <v>5.506296998867053</v>
       </c>
       <c r="N5" t="n">
-        <v>45.63198637681529</v>
+        <v>45.63259631143968</v>
       </c>
       <c r="O5" t="n">
-        <v>6.755145178070956</v>
+        <v>6.755190323850223</v>
       </c>
       <c r="P5" t="n">
-        <v>318.8227672462691</v>
+        <v>318.8682782506067</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -22061,28 +22125,28 @@
         <v>0.0629</v>
       </c>
       <c r="I6" t="n">
-        <v>0.337909987486359</v>
+        <v>0.3346502317758994</v>
       </c>
       <c r="J6" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K6" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1202758395209468</v>
+        <v>0.1187712473649895</v>
       </c>
       <c r="M6" t="n">
-        <v>5.505317442576069</v>
+        <v>5.503908518552068</v>
       </c>
       <c r="N6" t="n">
-        <v>44.31644225602758</v>
+        <v>44.26272194843703</v>
       </c>
       <c r="O6" t="n">
-        <v>6.657059580327306</v>
+        <v>6.653023519305867</v>
       </c>
       <c r="P6" t="n">
-        <v>319.4159190427643</v>
+        <v>319.4506531686687</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -22143,28 +22207,28 @@
         <v>0.0572</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2596755270468147</v>
+        <v>0.2573255575873205</v>
       </c>
       <c r="J7" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K7" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08671917387932193</v>
+        <v>0.08574397526701505</v>
       </c>
       <c r="M7" t="n">
-        <v>4.929588303634196</v>
+        <v>4.925735198061595</v>
       </c>
       <c r="N7" t="n">
-        <v>37.68304250784269</v>
+        <v>37.61045413704497</v>
       </c>
       <c r="O7" t="n">
-        <v>6.138651521942151</v>
+        <v>6.132736268342621</v>
       </c>
       <c r="P7" t="n">
-        <v>322.6233441895928</v>
+        <v>322.6483841442175</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -22225,28 +22289,28 @@
         <v>0.0582</v>
       </c>
       <c r="I8" t="n">
-        <v>0.250167560546584</v>
+        <v>0.2472865088514812</v>
       </c>
       <c r="J8" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K8" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08474282935027777</v>
+        <v>0.08335616065178575</v>
       </c>
       <c r="M8" t="n">
-        <v>4.814527527271404</v>
+        <v>4.813234972694913</v>
       </c>
       <c r="N8" t="n">
-        <v>35.86715059067126</v>
+        <v>35.82137758485231</v>
       </c>
       <c r="O8" t="n">
-        <v>5.988918983478676</v>
+        <v>5.985096288686784</v>
       </c>
       <c r="P8" t="n">
-        <v>325.663617731466</v>
+        <v>325.694316600094</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -22307,28 +22371,28 @@
         <v>0.0604</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2970123531526984</v>
+        <v>0.2951180424909328</v>
       </c>
       <c r="J9" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K9" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1237328081968534</v>
+        <v>0.1230084867643659</v>
       </c>
       <c r="M9" t="n">
-        <v>4.664964075179255</v>
+        <v>4.659504103346464</v>
       </c>
       <c r="N9" t="n">
-        <v>33.15090706484192</v>
+        <v>33.07732297661256</v>
       </c>
       <c r="O9" t="n">
-        <v>5.757682438693708</v>
+        <v>5.751288810050541</v>
       </c>
       <c r="P9" t="n">
-        <v>333.4100459812608</v>
+        <v>333.4302306916722</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -22389,28 +22453,28 @@
         <v>0.0692</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3392442597171384</v>
+        <v>0.3350161049722656</v>
       </c>
       <c r="J10" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K10" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1413389931012993</v>
+        <v>0.1387081527546765</v>
       </c>
       <c r="M10" t="n">
-        <v>4.815708737516428</v>
+        <v>4.82446954093036</v>
       </c>
       <c r="N10" t="n">
-        <v>37.10047522626132</v>
+        <v>37.1242966476317</v>
       </c>
       <c r="O10" t="n">
-        <v>6.091015943687992</v>
+        <v>6.092971085409129</v>
       </c>
       <c r="P10" t="n">
-        <v>330.5594671645045</v>
+        <v>330.6045200065872</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -22471,28 +22535,28 @@
         <v>0.06469999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2834465560765259</v>
+        <v>0.2800979753386479</v>
       </c>
       <c r="J11" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K11" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1098160550705977</v>
+        <v>0.1079408655271564</v>
       </c>
       <c r="M11" t="n">
-        <v>4.589358186008998</v>
+        <v>4.592820238675078</v>
       </c>
       <c r="N11" t="n">
-        <v>34.55819068940097</v>
+        <v>34.538717214877</v>
       </c>
       <c r="O11" t="n">
-        <v>5.878621495674047</v>
+        <v>5.876964966279534</v>
       </c>
       <c r="P11" t="n">
-        <v>336.2346331230275</v>
+        <v>336.2703137185326</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -22553,28 +22617,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2476423438851025</v>
+        <v>0.2436818638196377</v>
       </c>
       <c r="J12" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K12" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L12" t="n">
-        <v>0.08962580557252731</v>
+        <v>0.08729137027801082</v>
       </c>
       <c r="M12" t="n">
-        <v>4.611851245232446</v>
+        <v>4.619562223135263</v>
       </c>
       <c r="N12" t="n">
-        <v>33.05456048931903</v>
+        <v>33.07392804921584</v>
       </c>
       <c r="O12" t="n">
-        <v>5.749309566314814</v>
+        <v>5.750993657553088</v>
       </c>
       <c r="P12" t="n">
-        <v>341.7112333877532</v>
+        <v>341.7534340388001</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -22635,28 +22699,28 @@
         <v>0.06759999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2227049228688227</v>
+        <v>0.2196437245534614</v>
       </c>
       <c r="J13" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K13" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L13" t="n">
-        <v>0.06223364805414089</v>
+        <v>0.0609296744392076</v>
       </c>
       <c r="M13" t="n">
-        <v>5.035542623393758</v>
+        <v>5.036332626015045</v>
       </c>
       <c r="N13" t="n">
-        <v>39.65735356903618</v>
+        <v>39.60822446927792</v>
       </c>
       <c r="O13" t="n">
-        <v>6.297408480401774</v>
+        <v>6.293506532075575</v>
       </c>
       <c r="P13" t="n">
-        <v>352.4440600166358</v>
+        <v>352.476678426464</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -22717,28 +22781,28 @@
         <v>0.0663</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1013969418365065</v>
+        <v>0.09891346233105958</v>
       </c>
       <c r="J14" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K14" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01243268517145313</v>
+        <v>0.01190673079064486</v>
       </c>
       <c r="M14" t="n">
-        <v>5.306556474683248</v>
+        <v>5.303523231712728</v>
       </c>
       <c r="N14" t="n">
-        <v>43.33573767971961</v>
+        <v>43.25085831900307</v>
       </c>
       <c r="O14" t="n">
-        <v>6.582988506728507</v>
+        <v>6.576538475444591</v>
       </c>
       <c r="P14" t="n">
-        <v>346.467316584009</v>
+        <v>346.493779146693</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -22799,28 +22863,28 @@
         <v>0.0717</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1819745643163033</v>
+        <v>0.1778748299379564</v>
       </c>
       <c r="J15" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K15" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03259997699322081</v>
+        <v>0.03132790178869171</v>
       </c>
       <c r="M15" t="n">
-        <v>5.874302033435</v>
+        <v>5.878799672705923</v>
       </c>
       <c r="N15" t="n">
-        <v>52.14406506977437</v>
+        <v>52.11383018812726</v>
       </c>
       <c r="O15" t="n">
-        <v>7.221084757138249</v>
+        <v>7.218990939745475</v>
       </c>
       <c r="P15" t="n">
-        <v>344.4632264520606</v>
+        <v>344.506910918849</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -22862,7 +22926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P328"/>
+  <dimension ref="A1:P329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49761,6 +49825,88 @@
         </is>
       </c>
     </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>-35.44056215520937,174.4141530881756</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>-35.440296312669936,174.41499427718674</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>-35.43999720604771,174.41584193776006</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>-35.439633509256716,174.41668696814028</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>-35.43927935617206,174.41751656298845</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>-35.43890286159487,174.41830488587436</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>-35.43850174376237,174.4190685637613</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>-35.43802788016081,174.41979439695922</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>-35.437558232651675,174.42052127432987</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>-35.43701203858044,174.42114254346743</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>-35.43643925747414,174.42172289367988</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>-35.435808480894856,174.42222608295768</t>
+        </is>
+      </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>-35.435150738847994,174.4226697627694</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>-35.4344805466377,174.4230348811335</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0074/nzd0074.xlsx
+++ b/data/nzd0074/nzd0074.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P329"/>
+  <dimension ref="A1:P331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18222,6 +18222,114 @@
       <c r="P329" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>292.41</v>
+      </c>
+      <c r="C330" t="n">
+        <v>301.37</v>
+      </c>
+      <c r="D330" t="n">
+        <v>311.81</v>
+      </c>
+      <c r="E330" t="n">
+        <v>323.9</v>
+      </c>
+      <c r="F330" t="n">
+        <v>325.09</v>
+      </c>
+      <c r="G330" t="n">
+        <v>327.95</v>
+      </c>
+      <c r="H330" t="n">
+        <v>328.66</v>
+      </c>
+      <c r="I330" t="n">
+        <v>339.12</v>
+      </c>
+      <c r="J330" t="n">
+        <v>333.16</v>
+      </c>
+      <c r="K330" t="n">
+        <v>340.41</v>
+      </c>
+      <c r="L330" t="n">
+        <v>343.58</v>
+      </c>
+      <c r="M330" t="n">
+        <v>355.05</v>
+      </c>
+      <c r="N330" t="n">
+        <v>346.85</v>
+      </c>
+      <c r="O330" t="n">
+        <v>343.72</v>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>292.41</v>
+      </c>
+      <c r="C331" t="n">
+        <v>301.37</v>
+      </c>
+      <c r="D331" t="n">
+        <v>311.81</v>
+      </c>
+      <c r="E331" t="n">
+        <v>323.9</v>
+      </c>
+      <c r="F331" t="n">
+        <v>323.99</v>
+      </c>
+      <c r="G331" t="n">
+        <v>326.58</v>
+      </c>
+      <c r="H331" t="n">
+        <v>327.85</v>
+      </c>
+      <c r="I331" t="n">
+        <v>337.91</v>
+      </c>
+      <c r="J331" t="n">
+        <v>332.18</v>
+      </c>
+      <c r="K331" t="n">
+        <v>339.48</v>
+      </c>
+      <c r="L331" t="n">
+        <v>342.44</v>
+      </c>
+      <c r="M331" t="n">
+        <v>354.62</v>
+      </c>
+      <c r="N331" t="n">
+        <v>346.69</v>
+      </c>
+      <c r="O331" t="n">
+        <v>345.03</v>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -18236,7 +18344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B339"/>
+  <dimension ref="A1:B341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21629,6 +21737,26 @@
       </c>
       <c r="B339" t="n">
         <v>0.97</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>-0.08</v>
       </c>
     </row>
   </sheetData>
@@ -21797,28 +21925,28 @@
         <v>0.0716</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2923281490942704</v>
+        <v>0.281437295793597</v>
       </c>
       <c r="J2" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K2" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05780677962606839</v>
+        <v>0.05420663590558294</v>
       </c>
       <c r="M2" t="n">
-        <v>6.945751747697572</v>
+        <v>6.952023427433993</v>
       </c>
       <c r="N2" t="n">
-        <v>74.19608475627825</v>
+        <v>74.19982089572152</v>
       </c>
       <c r="O2" t="n">
-        <v>8.613714921929924</v>
+        <v>8.613931790751627</v>
       </c>
       <c r="P2" t="n">
-        <v>293.3638566155071</v>
+        <v>293.4805811895135</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -21879,28 +22007,28 @@
         <v>0.0572</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3606227312688297</v>
+        <v>0.3488768794052584</v>
       </c>
       <c r="J3" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K3" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09737902865459824</v>
+        <v>0.09218860089990866</v>
       </c>
       <c r="M3" t="n">
-        <v>6.269840903832529</v>
+        <v>6.286615294713299</v>
       </c>
       <c r="N3" t="n">
-        <v>64.21325631936371</v>
+        <v>64.35147968921059</v>
       </c>
       <c r="O3" t="n">
-        <v>8.013317435329997</v>
+        <v>8.021937402473956</v>
       </c>
       <c r="P3" t="n">
-        <v>301.1955251219367</v>
+        <v>301.3214132915567</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -21961,28 +22089,28 @@
         <v>0.0587</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3586834397178385</v>
+        <v>0.3465909090296966</v>
       </c>
       <c r="J4" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K4" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1133436466664506</v>
+        <v>0.1069662237843606</v>
       </c>
       <c r="M4" t="n">
-        <v>5.911349051592515</v>
+        <v>5.930379578607946</v>
       </c>
       <c r="N4" t="n">
-        <v>53.61166767334182</v>
+        <v>53.84573464197884</v>
       </c>
       <c r="O4" t="n">
-        <v>7.321998885095642</v>
+        <v>7.337965293048124</v>
       </c>
       <c r="P4" t="n">
-        <v>311.9612549412628</v>
+        <v>312.090858699454</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -22043,28 +22171,28 @@
         <v>0.0596</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3813353252334165</v>
+        <v>0.3749479487530311</v>
       </c>
       <c r="J5" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K5" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1451186575622336</v>
+        <v>0.1422557030377986</v>
       </c>
       <c r="M5" t="n">
-        <v>5.506296998867053</v>
+        <v>5.503078465325785</v>
       </c>
       <c r="N5" t="n">
-        <v>45.63259631143968</v>
+        <v>45.51199452217547</v>
       </c>
       <c r="O5" t="n">
-        <v>6.755190323850223</v>
+        <v>6.746257816165602</v>
       </c>
       <c r="P5" t="n">
-        <v>318.8682782506067</v>
+        <v>318.9367360590595</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -22125,28 +22253,28 @@
         <v>0.0629</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3346502317758994</v>
+        <v>0.3298892190474417</v>
       </c>
       <c r="J6" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K6" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1187712473649895</v>
+        <v>0.1170324112377713</v>
       </c>
       <c r="M6" t="n">
-        <v>5.503908518552068</v>
+        <v>5.492739614604656</v>
       </c>
       <c r="N6" t="n">
-        <v>44.26272194843703</v>
+        <v>44.08294562257264</v>
       </c>
       <c r="O6" t="n">
-        <v>6.653023519305867</v>
+        <v>6.639498898454057</v>
       </c>
       <c r="P6" t="n">
-        <v>319.4506531686687</v>
+        <v>319.5016834526644</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -22207,28 +22335,28 @@
         <v>0.0572</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2573255575873205</v>
+        <v>0.2545446614596041</v>
       </c>
       <c r="J7" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K7" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08574397526701505</v>
+        <v>0.08506825989207534</v>
       </c>
       <c r="M7" t="n">
-        <v>4.925735198061595</v>
+        <v>4.908851529504298</v>
       </c>
       <c r="N7" t="n">
-        <v>37.61045413704497</v>
+        <v>37.41492530446747</v>
       </c>
       <c r="O7" t="n">
-        <v>6.132736268342621</v>
+        <v>6.116774092973147</v>
       </c>
       <c r="P7" t="n">
-        <v>322.6483841442175</v>
+        <v>322.6781930023477</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -22289,28 +22417,28 @@
         <v>0.0582</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2472865088514812</v>
+        <v>0.2422689783441141</v>
       </c>
       <c r="J8" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K8" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08335616065178575</v>
+        <v>0.08110893326793778</v>
       </c>
       <c r="M8" t="n">
-        <v>4.813234972694913</v>
+        <v>4.806963564445326</v>
       </c>
       <c r="N8" t="n">
-        <v>35.82137758485231</v>
+        <v>35.70152003315849</v>
       </c>
       <c r="O8" t="n">
-        <v>5.985096288686784</v>
+        <v>5.975074897702831</v>
       </c>
       <c r="P8" t="n">
-        <v>325.694316600094</v>
+        <v>325.7480952981641</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -22371,28 +22499,28 @@
         <v>0.0604</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2951180424909328</v>
+        <v>0.2916642479264235</v>
       </c>
       <c r="J9" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K9" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1230084867643659</v>
+        <v>0.1218213244881956</v>
       </c>
       <c r="M9" t="n">
-        <v>4.659504103346464</v>
+        <v>4.646908194919</v>
       </c>
       <c r="N9" t="n">
-        <v>33.07732297661256</v>
+        <v>32.92469156055288</v>
       </c>
       <c r="O9" t="n">
-        <v>5.751288810050541</v>
+        <v>5.738004144347831</v>
       </c>
       <c r="P9" t="n">
-        <v>333.4302306916722</v>
+        <v>333.4672509850952</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -22453,28 +22581,28 @@
         <v>0.0692</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3350161049722656</v>
+        <v>0.3264678039573682</v>
       </c>
       <c r="J10" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K10" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1387081527546765</v>
+        <v>0.1333810905006264</v>
       </c>
       <c r="M10" t="n">
-        <v>4.82446954093036</v>
+        <v>4.842115909474284</v>
       </c>
       <c r="N10" t="n">
-        <v>37.1242966476317</v>
+        <v>37.18008382394228</v>
       </c>
       <c r="O10" t="n">
-        <v>6.092971085409129</v>
+        <v>6.097547361352946</v>
       </c>
       <c r="P10" t="n">
-        <v>330.6045200065872</v>
+        <v>330.6961408403595</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -22535,28 +22663,28 @@
         <v>0.06469999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2800979753386479</v>
+        <v>0.2753821471957038</v>
       </c>
       <c r="J11" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K11" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1079408655271564</v>
+        <v>0.1057912342395378</v>
       </c>
       <c r="M11" t="n">
-        <v>4.592820238675078</v>
+        <v>4.589497386356857</v>
       </c>
       <c r="N11" t="n">
-        <v>34.538717214877</v>
+        <v>34.4156957898541</v>
       </c>
       <c r="O11" t="n">
-        <v>5.876964966279534</v>
+        <v>5.866489221830557</v>
       </c>
       <c r="P11" t="n">
-        <v>336.2703137185326</v>
+        <v>336.3208591980395</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -22617,28 +22745,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2436818638196377</v>
+        <v>0.2371611717728228</v>
       </c>
       <c r="J12" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K12" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L12" t="n">
-        <v>0.08729137027801082</v>
+        <v>0.0837497676519291</v>
       </c>
       <c r="M12" t="n">
-        <v>4.619562223135263</v>
+        <v>4.62675162349602</v>
       </c>
       <c r="N12" t="n">
-        <v>33.07392804921584</v>
+        <v>33.03797448343671</v>
       </c>
       <c r="O12" t="n">
-        <v>5.750993657553088</v>
+        <v>5.747866950742398</v>
       </c>
       <c r="P12" t="n">
-        <v>341.7534340388001</v>
+        <v>341.823324100271</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -22699,28 +22827,28 @@
         <v>0.06759999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2196437245534614</v>
+        <v>0.2152930235766006</v>
       </c>
       <c r="J13" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K13" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0609296744392076</v>
+        <v>0.05935220601137603</v>
       </c>
       <c r="M13" t="n">
-        <v>5.036332626015045</v>
+        <v>5.028612329780676</v>
       </c>
       <c r="N13" t="n">
-        <v>39.60822446927792</v>
+        <v>39.44081144799634</v>
       </c>
       <c r="O13" t="n">
-        <v>6.293506532075575</v>
+        <v>6.280191991332457</v>
       </c>
       <c r="P13" t="n">
-        <v>352.476678426464</v>
+        <v>352.52330910742</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -22781,28 +22909,28 @@
         <v>0.0663</v>
       </c>
       <c r="I14" t="n">
-        <v>0.09891346233105958</v>
+        <v>0.09597173264741349</v>
       </c>
       <c r="J14" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K14" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01190673079064486</v>
+        <v>0.01136396185125221</v>
       </c>
       <c r="M14" t="n">
-        <v>5.303523231712728</v>
+        <v>5.286767531676687</v>
       </c>
       <c r="N14" t="n">
-        <v>43.25085831900307</v>
+        <v>43.02185111149446</v>
       </c>
       <c r="O14" t="n">
-        <v>6.576538475444591</v>
+        <v>6.559104444319702</v>
       </c>
       <c r="P14" t="n">
-        <v>346.493779146693</v>
+        <v>346.5253081243916</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -22863,28 +22991,28 @@
         <v>0.0717</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1778748299379564</v>
+        <v>0.1718120134444384</v>
       </c>
       <c r="J15" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K15" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03132790178869171</v>
+        <v>0.0296099560780303</v>
       </c>
       <c r="M15" t="n">
-        <v>5.878799672705923</v>
+        <v>5.876132818176776</v>
       </c>
       <c r="N15" t="n">
-        <v>52.11383018812726</v>
+        <v>51.94112778023347</v>
       </c>
       <c r="O15" t="n">
-        <v>7.218990939745475</v>
+        <v>7.207019340908797</v>
       </c>
       <c r="P15" t="n">
-        <v>344.506910918849</v>
+        <v>344.5718862482944</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -22926,7 +23054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P329"/>
+  <dimension ref="A1:P331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49907,6 +50035,170 @@
         </is>
       </c>
     </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>-35.44052764639967,174.41414108554062</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>-35.44025642818467,174.41498040458325</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>-35.43996875684369,174.4158309377131</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>-35.439619700107166,174.4166796406533</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>-35.439264134589735,174.417506494494</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>-35.438885869653554,174.41829260265925</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>-35.438494408518686,174.41906295197506</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>-35.438021724856505,174.41978863722903</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>-35.43755593904087,174.42051862675837</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>-35.43699957223625,174.4211266274778</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>-35.43642970575045,174.42170939485038</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>-35.43580107422351,174.42221121706586</t>
+        </is>
+      </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>-35.43514516534473,174.4226529119779</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>-35.434477321075704,174.42302495004563</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>-35.44052764639967,174.41414108554062</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>-35.44025642818467,174.41498040458325</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>-35.43996875684369,174.4158309377131</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>-35.439619700107166,174.4166796406533</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>-35.43927285528806,174.4175122629018</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>-35.438896499315646,174.41830028667903</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>-35.438500597630565,174.41906768691965</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>-35.43803038522643,174.4197967410357</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>-35.437562361150995,174.420526039959</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>-35.43700536908657,174.42113402841238</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>-35.436436427333945,174.42171889402638</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>-35.435803089963365,174.4222152628463</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>-35.43514570580575,174.42265454599394</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>-35.43447296490302,174.42301153795913</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0074/nzd0074.xlsx
+++ b/data/nzd0074/nzd0074.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P331"/>
+  <dimension ref="A1:P333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18328,6 +18328,114 @@
         <v>345.03</v>
       </c>
       <c r="P331" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>292.16</v>
+      </c>
+      <c r="C332" t="n">
+        <v>299.96</v>
+      </c>
+      <c r="D332" t="n">
+        <v>310.06</v>
+      </c>
+      <c r="E332" t="n">
+        <v>321.61</v>
+      </c>
+      <c r="F332" t="n">
+        <v>322.45</v>
+      </c>
+      <c r="G332" t="n">
+        <v>324.17</v>
+      </c>
+      <c r="H332" t="n">
+        <v>325.04</v>
+      </c>
+      <c r="I332" t="n">
+        <v>335.84</v>
+      </c>
+      <c r="J332" t="n">
+        <v>330.87</v>
+      </c>
+      <c r="K332" t="n">
+        <v>337.12</v>
+      </c>
+      <c r="L332" t="n">
+        <v>341.24</v>
+      </c>
+      <c r="M332" t="n">
+        <v>352.84</v>
+      </c>
+      <c r="N332" t="n">
+        <v>344.69</v>
+      </c>
+      <c r="O332" t="n">
+        <v>342.43</v>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>291.89</v>
+      </c>
+      <c r="C333" t="n">
+        <v>300.17</v>
+      </c>
+      <c r="D333" t="n">
+        <v>309.93</v>
+      </c>
+      <c r="E333" t="n">
+        <v>322.15</v>
+      </c>
+      <c r="F333" t="n">
+        <v>322.31</v>
+      </c>
+      <c r="G333" t="n">
+        <v>323.22</v>
+      </c>
+      <c r="H333" t="n">
+        <v>324.26</v>
+      </c>
+      <c r="I333" t="n">
+        <v>334.07</v>
+      </c>
+      <c r="J333" t="n">
+        <v>328.61</v>
+      </c>
+      <c r="K333" t="n">
+        <v>336.13</v>
+      </c>
+      <c r="L333" t="n">
+        <v>340.01</v>
+      </c>
+      <c r="M333" t="n">
+        <v>352.04</v>
+      </c>
+      <c r="N333" t="n">
+        <v>343.34</v>
+      </c>
+      <c r="O333" t="n">
+        <v>341.04</v>
+      </c>
+      <c r="P333" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -18344,7 +18452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B341"/>
+  <dimension ref="A1:B343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21757,6 +21865,26 @@
       </c>
       <c r="B341" t="n">
         <v>-0.08</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>0.83</v>
       </c>
     </row>
   </sheetData>
@@ -21925,28 +22053,28 @@
         <v>0.0716</v>
       </c>
       <c r="I2" t="n">
-        <v>0.281437295793597</v>
+        <v>0.2703808814621445</v>
       </c>
       <c r="J2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05420663590558294</v>
+        <v>0.05059404092096909</v>
       </c>
       <c r="M2" t="n">
-        <v>6.952023427433993</v>
+        <v>6.958760248027577</v>
       </c>
       <c r="N2" t="n">
-        <v>74.19982089572152</v>
+        <v>74.22873331378894</v>
       </c>
       <c r="O2" t="n">
-        <v>8.613931790751627</v>
+        <v>8.615609863137312</v>
       </c>
       <c r="P2" t="n">
-        <v>293.4805811895135</v>
+        <v>293.5995040725124</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -22007,28 +22135,28 @@
         <v>0.0572</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3488768794052584</v>
+        <v>0.3358476152874177</v>
       </c>
       <c r="J3" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K3" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09218860089990866</v>
+        <v>0.08629032934201097</v>
       </c>
       <c r="M3" t="n">
-        <v>6.286615294713299</v>
+        <v>6.309316441457483</v>
       </c>
       <c r="N3" t="n">
-        <v>64.35147968921059</v>
+        <v>64.62464011256411</v>
       </c>
       <c r="O3" t="n">
-        <v>8.021937402473956</v>
+        <v>8.038945211441867</v>
       </c>
       <c r="P3" t="n">
-        <v>301.3214132915567</v>
+        <v>301.461554612525</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -22089,28 +22217,28 @@
         <v>0.0587</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3465909090296966</v>
+        <v>0.3326091986476284</v>
       </c>
       <c r="J4" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K4" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1069662237843606</v>
+        <v>0.09932244414816194</v>
       </c>
       <c r="M4" t="n">
-        <v>5.930379578607946</v>
+        <v>5.957459028515529</v>
       </c>
       <c r="N4" t="n">
-        <v>53.84573464197884</v>
+        <v>54.28226476887217</v>
       </c>
       <c r="O4" t="n">
-        <v>7.337965293048124</v>
+        <v>7.367649880991372</v>
       </c>
       <c r="P4" t="n">
-        <v>312.090858699454</v>
+        <v>312.2412454754765</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -22171,28 +22299,28 @@
         <v>0.0596</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3749479487530311</v>
+        <v>0.3662401022223533</v>
       </c>
       <c r="J5" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K5" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1422557030377986</v>
+        <v>0.1374796667054204</v>
       </c>
       <c r="M5" t="n">
-        <v>5.503078465325785</v>
+        <v>5.510785356797533</v>
       </c>
       <c r="N5" t="n">
-        <v>45.51199452217547</v>
+        <v>45.5334093189505</v>
       </c>
       <c r="O5" t="n">
-        <v>6.746257816165602</v>
+        <v>6.747844790668388</v>
       </c>
       <c r="P5" t="n">
-        <v>318.9367360590595</v>
+        <v>319.0303954955859</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -22253,28 +22381,28 @@
         <v>0.0629</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3298892190474417</v>
+        <v>0.3225778574358493</v>
       </c>
       <c r="J6" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K6" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1170324112377713</v>
+        <v>0.1133877819990157</v>
       </c>
       <c r="M6" t="n">
-        <v>5.492739614604656</v>
+        <v>5.493762382017795</v>
       </c>
       <c r="N6" t="n">
-        <v>44.08294562257264</v>
+        <v>44.02547623998623</v>
       </c>
       <c r="O6" t="n">
-        <v>6.639498898454057</v>
+        <v>6.635169646662113</v>
       </c>
       <c r="P6" t="n">
-        <v>319.5016834526644</v>
+        <v>319.580324423254</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -22335,28 +22463,28 @@
         <v>0.0572</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2545446614596041</v>
+        <v>0.2474206688971908</v>
       </c>
       <c r="J7" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K7" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08506825989207534</v>
+        <v>0.08138358960261971</v>
       </c>
       <c r="M7" t="n">
-        <v>4.908851529504298</v>
+        <v>4.912356600877001</v>
       </c>
       <c r="N7" t="n">
-        <v>37.41492530446747</v>
+        <v>37.38839447919256</v>
       </c>
       <c r="O7" t="n">
-        <v>6.116774092973147</v>
+        <v>6.114605014160158</v>
       </c>
       <c r="P7" t="n">
-        <v>322.6781930023477</v>
+        <v>322.754821029734</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -22417,28 +22545,28 @@
         <v>0.0582</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2422689783441141</v>
+        <v>0.2329462515712417</v>
       </c>
       <c r="J8" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K8" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08110893326793778</v>
+        <v>0.07574870242839382</v>
       </c>
       <c r="M8" t="n">
-        <v>4.806963564445326</v>
+        <v>4.820825118406927</v>
       </c>
       <c r="N8" t="n">
-        <v>35.70152003315849</v>
+        <v>35.82562938876898</v>
       </c>
       <c r="O8" t="n">
-        <v>5.975074897702831</v>
+        <v>5.985451477438355</v>
       </c>
       <c r="P8" t="n">
-        <v>325.7480952981641</v>
+        <v>325.8483722769349</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -22499,28 +22627,28 @@
         <v>0.0604</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2916642479264235</v>
+        <v>0.2838982935520221</v>
       </c>
       <c r="J9" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K9" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1218213244881956</v>
+        <v>0.116834565323983</v>
       </c>
       <c r="M9" t="n">
-        <v>4.646908194919</v>
+        <v>4.654938693035377</v>
       </c>
       <c r="N9" t="n">
-        <v>32.92469156055288</v>
+        <v>32.96581257745165</v>
       </c>
       <c r="O9" t="n">
-        <v>5.738004144347831</v>
+        <v>5.741586242272396</v>
       </c>
       <c r="P9" t="n">
-        <v>333.4672509850952</v>
+        <v>333.5507863972529</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -22581,28 +22709,28 @@
         <v>0.0692</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3264678039573682</v>
+        <v>0.3145464351551306</v>
       </c>
       <c r="J10" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K10" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1333810905006264</v>
+        <v>0.1248763197811883</v>
       </c>
       <c r="M10" t="n">
-        <v>4.842115909474284</v>
+        <v>4.880613361982941</v>
       </c>
       <c r="N10" t="n">
-        <v>37.18008382394228</v>
+        <v>37.51685151883935</v>
       </c>
       <c r="O10" t="n">
-        <v>6.097547361352946</v>
+        <v>6.125100123168546</v>
       </c>
       <c r="P10" t="n">
-        <v>330.6961408403595</v>
+        <v>330.8243730489477</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -22663,28 +22791,28 @@
         <v>0.06469999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2753821471957038</v>
+        <v>0.266696137108118</v>
       </c>
       <c r="J11" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K11" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1057912342395378</v>
+        <v>0.1003488530862248</v>
       </c>
       <c r="M11" t="n">
-        <v>4.589497386356857</v>
+        <v>4.606454101654837</v>
       </c>
       <c r="N11" t="n">
-        <v>34.4156957898541</v>
+        <v>34.503462541611</v>
       </c>
       <c r="O11" t="n">
-        <v>5.866489221830557</v>
+        <v>5.87396480595611</v>
       </c>
       <c r="P11" t="n">
-        <v>336.3208591980395</v>
+        <v>336.4142883043974</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -22745,28 +22873,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2371611717728228</v>
+        <v>0.2278778022271206</v>
       </c>
       <c r="J12" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K12" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0837497676519291</v>
+        <v>0.07807877129271634</v>
       </c>
       <c r="M12" t="n">
-        <v>4.62675162349602</v>
+        <v>4.648292854489101</v>
       </c>
       <c r="N12" t="n">
-        <v>33.03797448343671</v>
+        <v>33.17663955168577</v>
       </c>
       <c r="O12" t="n">
-        <v>5.747866950742398</v>
+        <v>5.759916627147113</v>
       </c>
       <c r="P12" t="n">
-        <v>341.823324100271</v>
+        <v>341.9231791056912</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -22827,28 +22955,28 @@
         <v>0.06759999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2152930235766006</v>
+        <v>0.208101947020411</v>
       </c>
       <c r="J13" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K13" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05935220601137603</v>
+        <v>0.05612766598897001</v>
       </c>
       <c r="M13" t="n">
-        <v>5.028612329780676</v>
+        <v>5.035497017473053</v>
       </c>
       <c r="N13" t="n">
-        <v>39.44081144799634</v>
+        <v>39.4054295105546</v>
       </c>
       <c r="O13" t="n">
-        <v>6.280191991332457</v>
+        <v>6.277374412169039</v>
       </c>
       <c r="P13" t="n">
-        <v>352.52330910742</v>
+        <v>352.6006582455914</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -22909,28 +23037,28 @@
         <v>0.0663</v>
       </c>
       <c r="I14" t="n">
-        <v>0.09597173264741349</v>
+        <v>0.08972553660008084</v>
       </c>
       <c r="J14" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K14" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01136396185125221</v>
+        <v>0.01004804899054779</v>
       </c>
       <c r="M14" t="n">
-        <v>5.286767531676687</v>
+        <v>5.287838975516117</v>
       </c>
       <c r="N14" t="n">
-        <v>43.02185111149446</v>
+        <v>42.91726180599906</v>
       </c>
       <c r="O14" t="n">
-        <v>6.559104444319702</v>
+        <v>6.551126758504911</v>
       </c>
       <c r="P14" t="n">
-        <v>346.5253081243916</v>
+        <v>346.5924958383839</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -22991,28 +23119,28 @@
         <v>0.0717</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1718120134444384</v>
+        <v>0.1626633573990748</v>
       </c>
       <c r="J15" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K15" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0296099560780303</v>
+        <v>0.02681628352397403</v>
       </c>
       <c r="M15" t="n">
-        <v>5.876132818176776</v>
+        <v>5.890245985287407</v>
       </c>
       <c r="N15" t="n">
-        <v>51.94112778023347</v>
+        <v>51.95689792003899</v>
       </c>
       <c r="O15" t="n">
-        <v>7.207019340908797</v>
+        <v>7.208113339844137</v>
       </c>
       <c r="P15" t="n">
-        <v>344.5718862482944</v>
+        <v>344.6702927718118</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -23054,7 +23182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P331"/>
+  <dimension ref="A1:P333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50199,6 +50327,170 @@
         </is>
       </c>
     </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>-35.44052981403853,174.41414183947464</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>-35.44026865364668,174.41498465683628</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>-35.4399837979638,174.4158367534469</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>-35.43963863600671,174.4166896885253</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>-35.43928506426519,174.41752033867482</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>-35.43891519820892,174.4183138038283</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>-35.438522068498514,174.4190841130911</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>-35.438045200899225,174.41981060457678</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>-35.43757094580764,174.42053594944332</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>-35.437020079371266,174.42115280928337</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>-35.436443502684156,174.4217288931607</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>-35.43581143418733,174.42223201049757</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>-35.43515246156671,174.42267497119633</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>-35.43448161074044,174.42303815736884</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>-35.44053215508849,174.41414265372345</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>-35.4402668328332,174.4149840235219</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>-35.43998491530414,174.41583718547295</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>-35.43963417077284,174.4166873191577</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>-35.439286174172175,174.41752107283617</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>-35.43892256914146,174.4183191321669</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>-35.438528028383125,174.41908867267048</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>-35.43805786937166,174.41982245891307</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>-35.43758575597663,174.42055304519988</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>-35.437026250210096,174.42116068770162</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>-35.43645075491721,174.4217391422752</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>-35.43581518439955,174.42223953753296</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>-35.43515702170334,174.4226887582098</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>-35.43448623293566,174.42305238851705</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
